--- a/target/test-classes/RegistrationData.xlsx
+++ b/target/test-classes/RegistrationData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t>Firstname</t>
   </si>
@@ -618,7 +618,7 @@
         <v>38</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
